--- a/task-reviews/tile/task_tile_count_color_count/task_tile_count_color_count.xlsx
+++ b/task-reviews/tile/task_tile_count_color_count/task_tile_count_color_count.xlsx
@@ -1815,12 +1815,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0000.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0000.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0000.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0000.json</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0021.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0021.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0021.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0021.json</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0011.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0011.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0011.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0011.json</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0018.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0018.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0018.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0018.json</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0004.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0004.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0004.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0004.json</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0024.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0024.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0024.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0024.json</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0003.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0003.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0003.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0003.json</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0023.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0023.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0023.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0023.json</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0017.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0017.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0017.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0017.json</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0001.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0001.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0001.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0001.json</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0006.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0006.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0006.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0006.json</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0013.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0013.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0013.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0013.json</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0015.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0015.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0015.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0015.json</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0005.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0005.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0005.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0005.json</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0009.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0009.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0009.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0009.json</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0010.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0010.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0010.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0010.json</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0007.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0007.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0007.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0007.json</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0019.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0019.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0019.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0019.json</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0014.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0014.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0014.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0014.json</t>
         </is>
       </c>
     </row>
@@ -3031,12 +3031,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0012.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0012.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0012.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0012.json</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0016.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0016.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0016.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0016.json</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0002.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0002.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0002.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0002.json</t>
         </is>
       </c>
     </row>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0008.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0008.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0008.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0008.json</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0022.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0022.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0022.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0022.json</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/images/default/0020.png</t>
+          <t>tile/task_tile_count_color_count/images/default/0020.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_count_color_count/data/default/0020.json</t>
+          <t>tile/task_tile_count_color_count/data/default/0020.json</t>
         </is>
       </c>
     </row>
